--- a/data/dividends_info_20261010.xlsx
+++ b/data/dividends_info_20261010.xlsx
@@ -522,12 +522,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>46.54499816894531</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.1933612709003129</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>156</v>
       </c>
@@ -710,12 +706,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>46.54499816894531</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1933612709003129</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>65</v>
       </c>
@@ -1462,12 +1454,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>46.54499816894531</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1933612709003129</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>-19</v>
       </c>
@@ -3286,7 +3274,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3296,14 +3284,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3320,7 +3308,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3330,7 +3318,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3410,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3427,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3444,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3466,14 +3454,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3478,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3495,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3517,14 +3505,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3534,14 +3522,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3551,14 +3539,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3575,7 +3563,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3592,7 +3580,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3609,7 +3597,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3626,7 +3614,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3636,14 +3624,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3660,7 +3648,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3670,14 +3658,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3694,7 +3682,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3711,7 +3699,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3716,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3745,7 +3733,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3755,14 +3743,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3779,7 +3767,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3796,7 +3784,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3830,7 +3818,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3847,7 +3835,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3864,7 +3852,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3881,7 +3869,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3891,14 +3879,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3915,7 +3903,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3932,7 +3920,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3949,7 +3937,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3959,14 +3947,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3976,14 +3964,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4010,14 +3998,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4027,14 +4015,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4068,7 +4056,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4085,7 +4073,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4102,7 +4090,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4112,7 +4100,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4129,14 +4117,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,14 +4134,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4163,14 +4151,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4187,7 +4175,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4225,180 +4213,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SECO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>